--- a/artfynd/A 62040-2021 artfynd.xlsx
+++ b/artfynd/A 62040-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62040-2021 artfynd.xlsx
+++ b/artfynd/A 62040-2021 artfynd.xlsx
@@ -1532,7 +1532,7 @@
         <v>99588274</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554650.27502766</v>
+        <v>554650</v>
       </c>
       <c r="R9" t="n">
-        <v>6697977.896460385</v>
+        <v>6697978</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -3873,7 +3873,7 @@
         <v>111469929</v>
       </c>
       <c r="B29" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554646.3468513897</v>
+        <v>554646</v>
       </c>
       <c r="R29" t="n">
-        <v>6697975.861129273</v>
+        <v>6697976</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3951,19 +3951,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 62040-2021 artfynd.xlsx
+++ b/artfynd/A 62040-2021 artfynd.xlsx
@@ -1532,7 +1532,7 @@
         <v>99588274</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>111469929</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 62040-2021 artfynd.xlsx
+++ b/artfynd/A 62040-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97314130</v>
+        <v>111469940</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554634.1681246548</v>
+        <v>554771</v>
       </c>
       <c r="R2" t="n">
-        <v>6697995.933409011</v>
+        <v>6698131</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,76 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97313700</v>
+        <v>111469957</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554715.5115387026</v>
+        <v>554705</v>
       </c>
       <c r="R3" t="n">
-        <v>6698114.738690407</v>
+        <v>6697952</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,76 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97314274</v>
+        <v>111469958</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554713.4784821643</v>
+        <v>554681</v>
       </c>
       <c r="R4" t="n">
-        <v>6698019.854228493</v>
+        <v>6698061</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97314112</v>
+        <v>111469938</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,48 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554652.1423989626</v>
+        <v>554758</v>
       </c>
       <c r="R5" t="n">
-        <v>6697985.335209699</v>
+        <v>6698156</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,55 +1045,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97313800</v>
+        <v>99588479</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1207,24 +1099,23 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554707.7598132609</v>
+        <v>554685</v>
       </c>
       <c r="R6" t="n">
-        <v>6698103.75326092</v>
+        <v>6698064</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,22 +1139,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På klibbtickeavrötad granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,49 +1174,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog, Jonas Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111469945</v>
+        <v>111469928</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1330,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554636.1917053028</v>
+        <v>554705</v>
       </c>
       <c r="R7" t="n">
-        <v>6697992.999640726</v>
+        <v>6697953</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1363,19 +1254,14 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,6 +1270,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1402,63 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99588479</v>
+        <v>111469926</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kyrkberget, Husby, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554684.1063969049</v>
+        <v>554746</v>
       </c>
       <c r="R8" t="n">
-        <v>6698064.368490165</v>
+        <v>6698078</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,27 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klibbtickeavrötad granlåga.</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,72 +1374,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Uno Skog, Jonas Eriksson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99588274</v>
+        <v>111469927</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kyrkberget, Husby, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554650</v>
+        <v>554731</v>
       </c>
       <c r="R9" t="n">
-        <v>6697978</v>
+        <v>6698165</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,27 +1451,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla ringspår i nydöd tall.</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,49 +1471,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111469951</v>
+        <v>111469969</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554679.0891228422</v>
+        <v>554769</v>
       </c>
       <c r="R10" t="n">
-        <v>6697970.425878088</v>
+        <v>6698130</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1726,27 +1551,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1765,53 +1581,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111469952</v>
+        <v>99588274</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554701.1291447466</v>
+        <v>554650</v>
       </c>
       <c r="R11" t="n">
-        <v>6697985.57934437</v>
+        <v>6697978</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,22 +1653,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringspår i nydöd tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,58 +1688,52 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111469968</v>
+        <v>111469929</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1926,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554679.218646974</v>
+        <v>554646</v>
       </c>
       <c r="R12" t="n">
-        <v>6698060.342582431</v>
+        <v>6697976</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1959,28 +1776,17 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1999,53 +1805,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111469958</v>
+        <v>99588518</v>
       </c>
       <c r="B13" t="n">
-        <v>89621</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1101</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554681.1975678616</v>
+        <v>554723</v>
       </c>
       <c r="R13" t="n">
-        <v>6698060.372405332</v>
+        <v>6698090</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,22 +1877,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,62 +1907,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog, Jonas Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111469954</v>
+        <v>111469961</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554709.4759112563</v>
+        <v>554633</v>
       </c>
       <c r="R14" t="n">
-        <v>6698022.75809369</v>
+        <v>6697957</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2184,27 +1996,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2223,15 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111469922</v>
+        <v>111469962</v>
       </c>
       <c r="B15" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,7 +2060,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2272,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554716.6256586342</v>
+        <v>554640</v>
       </c>
       <c r="R15" t="n">
-        <v>6698008.044787553</v>
+        <v>6697989</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2305,19 +2103,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2345,15 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111469965</v>
+        <v>111469963</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2394,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554716.1509068209</v>
+        <v>554719</v>
       </c>
       <c r="R16" t="n">
-        <v>6698137.967376946</v>
+        <v>6698003</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2427,19 +2210,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,15 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111469966</v>
+        <v>111469964</v>
       </c>
       <c r="B17" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2274,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2516,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554729.2459973614</v>
+        <v>554732</v>
       </c>
       <c r="R17" t="n">
-        <v>6698057.144588907</v>
+        <v>6698141</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2549,19 +2317,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,15 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111469926</v>
+        <v>111469965</v>
       </c>
       <c r="B18" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,34 +2358,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554745.7538377594</v>
+        <v>554716</v>
       </c>
       <c r="R18" t="n">
-        <v>6698078.142900295</v>
+        <v>6698138</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2662,27 +2424,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2701,50 +2454,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111469953</v>
+        <v>111469966</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554668.8331894471</v>
+        <v>554729</v>
       </c>
       <c r="R19" t="n">
-        <v>6698027.085862564</v>
+        <v>6698057</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2774,27 +2531,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2813,15 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111469963</v>
+        <v>111469967</v>
       </c>
       <c r="B20" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,7 +2595,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2862,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554718.6790950731</v>
+        <v>554705</v>
       </c>
       <c r="R20" t="n">
-        <v>6698003.135367867</v>
+        <v>6698114</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2895,19 +2638,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,15 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111469964</v>
+        <v>111469968</v>
       </c>
       <c r="B21" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2702,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2984,10 +2712,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>554731.9372321201</v>
+        <v>554679</v>
       </c>
       <c r="R21" t="n">
-        <v>6698141.169601779</v>
+        <v>6698061</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3017,19 +2745,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3057,46 +2775,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111469962</v>
+        <v>111469934</v>
       </c>
       <c r="B22" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3106,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554640.2091243146</v>
+        <v>554729</v>
       </c>
       <c r="R22" t="n">
-        <v>6697989.107814683</v>
+        <v>6697999</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3139,28 +2851,17 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3179,53 +2880,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111469949</v>
+        <v>99588873</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554654.1362404823</v>
+        <v>554762</v>
       </c>
       <c r="R23" t="n">
-        <v>6697984.37715952</v>
+        <v>6698132</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3249,22 +2956,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,62 +2986,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Uno Skog, Jonas Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111469947</v>
+        <v>111469922</v>
       </c>
       <c r="B24" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554660.8096201464</v>
+        <v>554717</v>
       </c>
       <c r="R24" t="n">
-        <v>6698001.275046931</v>
+        <v>6698008</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3364,27 +3075,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3403,50 +3105,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111469950</v>
+        <v>111469923</v>
       </c>
       <c r="B25" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554648.2514272946</v>
+        <v>554704</v>
       </c>
       <c r="R25" t="n">
-        <v>6697980.830233379</v>
+        <v>6698141</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3476,27 +3182,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3515,62 +3212,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111469967</v>
+        <v>97313700</v>
       </c>
       <c r="B26" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554705.6319759471</v>
+        <v>554715</v>
       </c>
       <c r="R26" t="n">
-        <v>6698113.601669285</v>
+        <v>6698115</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3594,22 +3288,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3618,34 +3312,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111469941</v>
+        <v>97313800</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,28 +3358,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>554704.8063610581</v>
+        <v>554707</v>
       </c>
       <c r="R27" t="n">
-        <v>6698102.720679003</v>
+        <v>6698104</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3715,22 +3406,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,34 +3430,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111469944</v>
+        <v>97314112</v>
       </c>
       <c r="B28" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3791,20 +3476,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>554647.0313377964</v>
+        <v>554652</v>
       </c>
       <c r="R28" t="n">
-        <v>6697996.127116338</v>
+        <v>6697985</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3828,22 +3524,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3858,70 +3554,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111469929</v>
+        <v>111469945</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554646</v>
+        <v>554636</v>
       </c>
       <c r="R29" t="n">
-        <v>6697976</v>
+        <v>6697993</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3980,15 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111469946</v>
+        <v>97314130</v>
       </c>
       <c r="B30" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4013,20 +3691,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>554664.6782300239</v>
+        <v>554634</v>
       </c>
       <c r="R30" t="n">
-        <v>6698007.261790544</v>
+        <v>6697995</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4050,22 +3739,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4080,65 +3769,71 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111469969</v>
+        <v>97314274</v>
       </c>
       <c r="B31" t="n">
-        <v>76495</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>554769.2275642991</v>
+        <v>554713</v>
       </c>
       <c r="R31" t="n">
-        <v>6698129.381786803</v>
+        <v>6698020</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,22 +3857,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,69 +3881,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111469940</v>
+        <v>111469941</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>554771.1915359092</v>
+        <v>554705</v>
       </c>
       <c r="R32" t="n">
-        <v>6698130.399477887</v>
+        <v>6698102</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4278,27 +3975,18 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4314,6 +4002,879 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111469944</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>554647</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697996</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>111469946</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>554665</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6698007</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>111469947</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>554661</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6698001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>111469949</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>554654</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6697984</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111469950</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>554648</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6697981</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111469951</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>554679</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6697971</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111469952</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>554701</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6697986</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111469953</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>554669</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6698027</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111469954</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>554710</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6698023</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62040-2021 artfynd.xlsx
+++ b/artfynd/A 62040-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469957</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99588479</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469928</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469926</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469927</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469969</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99588274</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469929</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99588518</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469961</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469962</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469963</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469964</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469965</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469966</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469967</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469968</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469934</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99588873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3102,6 +3217,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469922</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469923</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3327,6 +3452,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97313700</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3445,6 +3575,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97313800</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3563,6 +3698,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97314112</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3660,6 +3800,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469945</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3778,6 +3923,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97314130</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3896,6 +4046,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97314274</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4002,6 +4157,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469941</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4099,6 +4259,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469944</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4196,6 +4361,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469946</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4293,6 +4463,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469947</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4390,6 +4565,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469949</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4487,6 +4667,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469950</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4584,6 +4769,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469951</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4681,6 +4871,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469952</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4778,6 +4973,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469953</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4875,8 +5075,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111469954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>